--- a/Result/profitability/2330.xlsx
+++ b/Result/profitability/2330.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM84"/>
+  <dimension ref="A1:AM85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,10 +667,10 @@
         <v>0.99</v>
       </c>
       <c r="M2" t="n">
-        <v>14.54125</v>
+        <v>16.37875</v>
       </c>
       <c r="N2" t="n">
-        <v>58.2725</v>
+        <v>59.50875000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -776,16 +776,16 @@
         <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>13.14375</v>
+        <v>14.74375</v>
       </c>
       <c r="N3" t="n">
-        <v>57.5625</v>
+        <v>58.6525</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -893,10 +893,10 @@
         <v>1.32</v>
       </c>
       <c r="M4" t="n">
-        <v>11.5025</v>
+        <v>13.165</v>
       </c>
       <c r="N4" t="n">
-        <v>56.245</v>
+        <v>57.36125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1010,10 +1010,10 @@
         <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>9.92375</v>
+        <v>11.41</v>
       </c>
       <c r="N5" t="n">
-        <v>55.365</v>
+        <v>56.5025</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>1.26</v>
       </c>
       <c r="M6" t="n">
-        <v>8.161250000000001</v>
+        <v>9.387500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>54.27125</v>
+        <v>55.305</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>1.08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.11625</v>
+        <v>7.08375</v>
       </c>
       <c r="N7" t="n">
-        <v>52.585</v>
+        <v>53.25875000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>0.73</v>
       </c>
       <c r="M8" t="n">
-        <v>3.76875</v>
+        <v>4.415000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>49.53375</v>
+        <v>49.7175</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2136,7 +2136,7 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>44.51</v>
+        <v>44.51000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -2517,7 +2517,7 @@
         <v>0.9187500000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>40.71</v>
+        <v>40.71000000000001</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -2644,7 +2644,7 @@
         <v>0.9225</v>
       </c>
       <c r="N18" t="n">
-        <v>40.94374999999999</v>
+        <v>40.94375</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -3025,7 +3025,7 @@
         <v>0.99625</v>
       </c>
       <c r="N21" t="n">
-        <v>42.04499999999999</v>
+        <v>42.045</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -11076,6 +11076,133 @@
       </c>
       <c r="AM84" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1270380</v>
+      </c>
+      <c r="D85" t="n">
+        <v>410070</v>
+      </c>
+      <c r="E85" t="n">
+        <v>860311</v>
+      </c>
+      <c r="F85" t="n">
+        <v>67.72</v>
+      </c>
+      <c r="G85" t="n">
+        <v>766603</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>60.34%</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>95827</v>
+      </c>
+      <c r="J85" t="n">
+        <v>862430</v>
+      </c>
+      <c r="K85" t="n">
+        <v>706562</v>
+      </c>
+      <c r="L85" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="M85" t="n">
+        <v>17.82375</v>
+      </c>
+      <c r="N85" t="n">
+        <v>61.24875</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W85" t="n">
+        <v>5.170000000000002</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0.2341485507246377</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1.469999999999999</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>0.02218867924528301</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0.7740885416666667</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>9.100000000000001</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>0.1552371204367111</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK85" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
